--- a/tiflow-diga/build/0.9.0/StructureDefinition-GEM-ERP-EX-RedeemCode.xlsx
+++ b/tiflow-diga/build/0.9.0/StructureDefinition-GEM-ERP-EX-RedeemCode.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/erp-diga/StructureDefinition/GEM_ERP_EX_RedeemCode</t>
+    <t>https://gematik.de/fhir/tiflow/diga/StructureDefinition/GEM_ERP_EX_RedeemCode</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06</t>
+    <t>2025-09-25</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1307,7 +1307,7 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>104</v>
